--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415043</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415042</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415043</v>
+        <v>127415042</v>
       </c>
       <c r="B2" t="n">
-        <v>98387</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588989</v>
+        <v>588982</v>
       </c>
       <c r="R2" t="n">
-        <v>6683598</v>
+        <v>6683581</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering, Fläcknycklar i sumpskog,</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering, Fläcknycklar spridd i sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415042</v>
+        <v>127415043</v>
       </c>
       <c r="B3" t="n">
-        <v>98387</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588982</v>
+        <v>588989</v>
       </c>
       <c r="R3" t="n">
-        <v>6683581</v>
+        <v>6683598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering, Fläcknycklar spridd i sumpskog</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering, Fläcknycklar i sumpskog,</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36002-2025 artfynd.xlsx
+++ b/artfynd/A 36002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>